--- a/Database Function.xlsx
+++ b/Database Function.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20375"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucky\Desktop\Advance Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F356C1-2E36-49D5-8C6D-4CAA64A8E402}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499A5884-567E-4284-8935-5B5308F00C33}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="7890" xr2:uid="{8F604947-E31D-4FA0-8B60-5715E0123833}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="74">
   <si>
     <t>Id</t>
   </si>
@@ -723,7 +723,7 @@
         <v>2</v>
       </c>
       <c r="N2" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="s">
         <v>4</v>
@@ -874,6 +874,9 @@
       <c r="J4" t="s">
         <v>21</v>
       </c>
+      <c r="M4" t="s">
+        <v>4</v>
+      </c>
       <c r="U4" t="s">
         <v>18</v>
       </c>
@@ -911,6 +914,13 @@
       </c>
       <c r="J5" t="s">
         <v>24</v>
+      </c>
+      <c r="M5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N5">
+        <f>DSUM(aa,N2,M7:M8)</f>
+        <v>251994</v>
       </c>
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.25">
